--- a/survey_templates/045_technology_survey_for_remote_learning--survey_templates.xlsx
+++ b/survey_templates/045_technology_survey_for_remote_learning--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote learning experience</t>
+          <t>Remote learning experience (2)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ease of use</t>
+          <t>Easy Of Use</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Support (2)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Additional comments</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Technology (2)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>page8</t>
+          <t>page8 (2)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>page9</t>
+          <t>page9_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>page9</t>
+          <t>Page9 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>page10</t>
+          <t>page10_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>page10</t>
+          <t>Page10 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>page11</t>
+          <t>page11_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>page11</t>
+          <t>Page11 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>page12</t>
+          <t>page12_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>page12</t>
+          <t>Page12 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_bad'}</t>
+          <t>very_bad</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very bad'}</t>
+          <t>Very bad</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'easy'}</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Easy'}</t>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'difficult'}</t>
+          <t>difficult</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Difficult'}</t>
+          <t>Difficult</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'very_bad'}</t>
+          <t>very_bad</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Very bad'}</t>
+          <t>Very bad</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
